--- a/outputs/holdout_70_30/pred_files_holdout.xlsx
+++ b/outputs/holdout_70_30/pred_files_holdout.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_ann.csv</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_rf.csv</t>
         </is>
       </c>
     </row>
@@ -475,29 +475,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_xgb.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>('corn', 'alkaline')</t>
+          <t>('corn', 'acid')</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_ann.csv</t>
         </is>
       </c>
     </row>
@@ -526,46 +526,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_xgb.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -577,19 +577,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_xgb.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_ann.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,14 +599,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -616,14 +616,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -633,167 +633,167 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_xgb.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_xgb.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_ann.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_xgb.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_xgb.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_ann.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_xgb.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_xgb.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>ann</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_xgb.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_ann.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -803,14 +803,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_rf.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -820,22 +820,158 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_svm.csv</t>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>('potato', 'alkaline')</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_xgb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_ann.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_rf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_svm.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_xgb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>('potato', 'strong_acid')</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_ann.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_rf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_svm.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>xgb</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_xgb.csv</t>
         </is>

--- a/outputs/holdout_70_30/pred_files_holdout.xlsx
+++ b/outputs/holdout_70_30/pred_files_holdout.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_ann.csv</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_rf.csv</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_svm.csv</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_acid_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_ann.csv</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_rf.csv</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_svm.csv</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_ann.csv</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_rf.csv</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_svm.csv</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_ann.csv</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_rf.csv</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_svm.csv</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_ann.csv</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_rf.csv</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_svm.csv</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_acid_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_ann.csv</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_rf.csv</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_svm.csv</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_ann.csv</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_rf.csv</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_svm.csv</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_ann.csv</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_rf.csv</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_svm.csv</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>..\outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_xgb.csv</t>
         </is>
       </c>
     </row>

--- a/outputs/holdout_70_30/pred_files_holdout.xlsx
+++ b/outputs/holdout_70_30/pred_files_holdout.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_catboost.csv</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_lightgbm.csv</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_rf.csv</t>
         </is>
       </c>
     </row>
@@ -492,29 +492,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>('corn', 'alkaline')</t>
+          <t>('corn', 'acid')</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_acid_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -526,12 +526,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_catboost.csv</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_lightgbm.csv</t>
         </is>
       </c>
     </row>
@@ -560,46 +560,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>('corn', 'neutral')</t>
+          <t>('corn', 'alkaline')</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_alkaline_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_catboost.csv</t>
         </is>
       </c>
     </row>
@@ -628,63 +628,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_lightgbm.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>('corn', 'strong_acid')</t>
+          <t>('corn', 'neutral')</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_neutral_xgb.csv</t>
         </is>
       </c>
     </row>
@@ -696,36 +696,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_catboost.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_lightgbm.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -752,14 +752,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>('potato', 'acid')</t>
+          <t>('corn', 'strong_acid')</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -769,209 +769,345 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_corn_strong_acid_xgb.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_catboost.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_lightgbm.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>('potato', 'alkaline')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'acid')</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_acid_xgb.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_catboost.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>lightgbm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_lightgbm.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>('potato', 'neutral')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_xgb.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_rf.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ann</t>
+          <t>svm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_ann.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_svm.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'alkaline')</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_rf.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_alkaline_xgb.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>('potato', 'strong_acid')</t>
+          <t>('potato', 'neutral')</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>svm</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_svm.csv</t>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_catboost.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>lightgbm</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_lightgbm.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_rf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_svm.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>('potato', 'neutral')</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_neutral_xgb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>('potato', 'strong_acid')</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>catboost</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_catboost.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>lightgbm</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_lightgbm.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_rf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>svm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_svm.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>('potato', 'strong_acid')</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>xgb</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>outputs\holdout_70_30\predictions\pred_holdout_potato_strong_acid_xgb.csv</t>
         </is>
